--- a/Result/profitability/4749.xlsx
+++ b/Result/profitability/4749.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM38"/>
+  <dimension ref="A1:AM39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.28</v>
       </c>
       <c r="M2" t="n">
-        <v>2.33875</v>
+        <v>2.51125</v>
       </c>
       <c r="N2" t="n">
-        <v>39.37</v>
+        <v>40.22875000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>2.13625</v>
+        <v>2.2825</v>
       </c>
       <c r="N3" t="n">
-        <v>37.77</v>
+        <v>38.5825</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.835</v>
+        <v>1.96</v>
       </c>
       <c r="N4" t="n">
-        <v>35.1525</v>
+        <v>35.83750000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.66</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4675</v>
+        <v>1.49375</v>
       </c>
       <c r="N5" t="n">
-        <v>32.14625</v>
+        <v>31.9325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -5256,6 +5256,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4749</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1233</v>
+      </c>
+      <c r="D39" t="n">
+        <v>684</v>
+      </c>
+      <c r="E39" t="n">
+        <v>549</v>
+      </c>
+      <c r="F39" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="G39" t="n">
+        <v>286</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>23.20%</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>75</v>
+      </c>
+      <c r="J39" t="n">
+        <v>361</v>
+      </c>
+      <c r="K39" t="n">
+        <v>304</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.78375</v>
+      </c>
+      <c r="N39" t="n">
+        <v>42.15125</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W39" t="n">
+        <v>-0.3800000000000003</v>
+      </c>
+      <c r="X39" t="n">
+        <v>-0.103825136612022</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-0.8799999999999955</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-0.01937899141158328</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.0684039087947883</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>-1.710000000000001</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>-0.03698096885813151</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK39" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
